--- a/source/8、绩效异常岗位/6、分拣岗/分拣岗-5月.xlsx
+++ b/source/8、绩效异常岗位/6、分拣岗/分拣岗-5月.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1578" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1702" uniqueCount="103">
   <si>
     <t>数据日期</t>
   </si>
@@ -332,6 +332,12 @@
   </si>
   <si>
     <t>2026-05-29</t>
+  </si>
+  <si>
+    <t>2026-05-30</t>
+  </si>
+  <si>
+    <t>2026-05-31</t>
   </si>
 </sst>
 </file>
@@ -1265,7 +1271,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H352"/>
+  <dimension ref="A1:H378"/>
   <sheetFormatPr defaultColWidth="12.6363636363636" defaultRowHeight="20" customHeight="1" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="16384" width="12.6363636363636" style="1" customWidth="1"/>
@@ -10421,6 +10427,682 @@
       </c>
       <c r="H352" s="1">
         <v>11</v>
+      </c>
+    </row>
+    <row r="353" customHeight="1" spans="1:8">
+      <c r="A353" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B353" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C353" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D353" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E353" s="1">
+        <v>123.2</v>
+      </c>
+      <c r="F353" s="1">
+        <v>70.1</v>
+      </c>
+      <c r="G353" s="1">
+        <v>110.2</v>
+      </c>
+      <c r="H353" s="1">
+        <v>11.7</v>
+      </c>
+    </row>
+    <row r="354" customHeight="1" spans="1:8">
+      <c r="A354" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B354" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C354" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D354" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E354" s="1">
+        <v>105.5</v>
+      </c>
+      <c r="F354" s="1">
+        <v>30.7</v>
+      </c>
+      <c r="G354" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H354" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="355" customHeight="1" spans="1:8">
+      <c r="A355" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B355" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C355" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D355" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E355" s="1">
+        <v>118.4</v>
+      </c>
+      <c r="F355" s="1">
+        <v>27.2</v>
+      </c>
+      <c r="G355" s="1">
+        <v>110.2</v>
+      </c>
+      <c r="H355" s="1">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="356" customHeight="1" spans="1:8">
+      <c r="A356" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B356" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C356" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D356" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E356" s="1">
+        <v>107.9</v>
+      </c>
+      <c r="F356" s="1">
+        <v>22</v>
+      </c>
+      <c r="G356" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H356" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="357" customHeight="1" spans="1:8">
+      <c r="A357" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B357" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C357" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D357" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E357" s="1">
+        <v>69.3</v>
+      </c>
+      <c r="F357" s="1">
+        <v>20.1</v>
+      </c>
+      <c r="G357" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H357" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="358" customHeight="1" spans="1:8">
+      <c r="A358" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B358" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C358" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D358" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E358" s="1">
+        <v>115.4</v>
+      </c>
+      <c r="F358" s="1">
+        <v>17.5</v>
+      </c>
+      <c r="G358" s="1">
+        <v>110.2</v>
+      </c>
+      <c r="H358" s="1">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="359" customHeight="1" spans="1:8">
+      <c r="A359" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B359" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C359" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D359" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E359" s="1">
+        <v>126.1</v>
+      </c>
+      <c r="F359" s="1">
+        <v>17.1</v>
+      </c>
+      <c r="G359" s="1">
+        <v>110.2</v>
+      </c>
+      <c r="H359" s="1">
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="360" customHeight="1" spans="1:8">
+      <c r="A360" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B360" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C360" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D360" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E360" s="1">
+        <v>107.6</v>
+      </c>
+      <c r="F360" s="1">
+        <v>13.1</v>
+      </c>
+      <c r="G360" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H360" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="361" customHeight="1" spans="1:8">
+      <c r="A361" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B361" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C361" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D361" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E361" s="1">
+        <v>61.8</v>
+      </c>
+      <c r="F361" s="1">
+        <v>12</v>
+      </c>
+      <c r="G361" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H361" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="362" customHeight="1" spans="1:8">
+      <c r="A362" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B362" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C362" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D362" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="E362" s="1">
+        <v>115.1</v>
+      </c>
+      <c r="F362" s="1">
+        <v>10.8</v>
+      </c>
+      <c r="G362" s="1">
+        <v>110.2</v>
+      </c>
+      <c r="H362" s="1">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="363" customHeight="1" spans="1:8">
+      <c r="A363" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B363" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C363" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D363" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E363" s="1">
+        <v>198.2</v>
+      </c>
+      <c r="F363" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="G363" s="1">
+        <v>110.2</v>
+      </c>
+      <c r="H363" s="1">
+        <v>79.7</v>
+      </c>
+    </row>
+    <row r="364" customHeight="1" spans="1:8">
+      <c r="A364" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B364" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C364" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D364" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E364" s="1">
+        <v>143.4</v>
+      </c>
+      <c r="F364" s="1">
+        <v>-1.8</v>
+      </c>
+      <c r="G364" s="1">
+        <v>110.2</v>
+      </c>
+      <c r="H364" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="365" customHeight="1" spans="1:8">
+      <c r="A365" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B365" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C365" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D365" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E365" s="1">
+        <v>122.3</v>
+      </c>
+      <c r="F365" s="1">
+        <v>-16.2</v>
+      </c>
+      <c r="G365" s="1">
+        <v>110.2</v>
+      </c>
+      <c r="H365" s="1">
+        <v>10.9</v>
+      </c>
+    </row>
+    <row r="366" customHeight="1" spans="1:8">
+      <c r="A366" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B366" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C366" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D366" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E366" s="1">
+        <v>123.1</v>
+      </c>
+      <c r="F366" s="1">
+        <v>70</v>
+      </c>
+      <c r="G366" s="1">
+        <v>110.1</v>
+      </c>
+      <c r="H366" s="1">
+        <v>11.8</v>
+      </c>
+    </row>
+    <row r="367" customHeight="1" spans="1:8">
+      <c r="A367" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B367" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C367" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D367" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E367" s="1">
+        <v>105.4</v>
+      </c>
+      <c r="F367" s="1">
+        <v>30.5</v>
+      </c>
+      <c r="G367" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H367" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="368" customHeight="1" spans="1:8">
+      <c r="A368" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B368" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C368" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D368" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E368" s="1">
+        <v>117.8</v>
+      </c>
+      <c r="F368" s="1">
+        <v>26.6</v>
+      </c>
+      <c r="G368" s="1">
+        <v>110.1</v>
+      </c>
+      <c r="H368" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="369" customHeight="1" spans="1:8">
+      <c r="A369" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B369" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C369" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D369" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E369" s="1">
+        <v>107.3</v>
+      </c>
+      <c r="F369" s="1">
+        <v>21.3</v>
+      </c>
+      <c r="G369" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H369" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="370" customHeight="1" spans="1:8">
+      <c r="A370" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B370" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C370" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D370" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E370" s="1">
+        <v>68.6</v>
+      </c>
+      <c r="F370" s="1">
+        <v>18.9</v>
+      </c>
+      <c r="G370" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H370" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="371" customHeight="1" spans="1:8">
+      <c r="A371" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B371" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C371" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D371" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E371" s="1">
+        <v>114.5</v>
+      </c>
+      <c r="F371" s="1">
+        <v>16.5</v>
+      </c>
+      <c r="G371" s="1">
+        <v>110.1</v>
+      </c>
+      <c r="H371" s="1">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="372" customHeight="1" spans="1:8">
+      <c r="A372" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B372" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C372" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D372" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E372" s="1">
+        <v>124.6</v>
+      </c>
+      <c r="F372" s="1">
+        <v>15.7</v>
+      </c>
+      <c r="G372" s="1">
+        <v>110.1</v>
+      </c>
+      <c r="H372" s="1">
+        <v>13.1</v>
+      </c>
+    </row>
+    <row r="373" customHeight="1" spans="1:8">
+      <c r="A373" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B373" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C373" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D373" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E373" s="1">
+        <v>107.1</v>
+      </c>
+      <c r="F373" s="1">
+        <v>12.7</v>
+      </c>
+      <c r="G373" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H373" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="374" customHeight="1" spans="1:8">
+      <c r="A374" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B374" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C374" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D374" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E374" s="1">
+        <v>62.1</v>
+      </c>
+      <c r="F374" s="1">
+        <v>12.4</v>
+      </c>
+      <c r="G374" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H374" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="375" customHeight="1" spans="1:8">
+      <c r="A375" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B375" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C375" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D375" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="E375" s="1">
+        <v>113</v>
+      </c>
+      <c r="F375" s="1">
+        <v>10</v>
+      </c>
+      <c r="G375" s="1">
+        <v>110.1</v>
+      </c>
+      <c r="H375" s="1">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="376" customHeight="1" spans="1:8">
+      <c r="A376" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B376" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C376" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D376" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E376" s="1">
+        <v>197.8</v>
+      </c>
+      <c r="F376" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="G376" s="1">
+        <v>110.1</v>
+      </c>
+      <c r="H376" s="1">
+        <v>79.5</v>
+      </c>
+    </row>
+    <row r="377" customHeight="1" spans="1:8">
+      <c r="A377" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B377" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C377" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D377" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E377" s="1">
+        <v>143.1</v>
+      </c>
+      <c r="F377" s="1">
+        <v>-2</v>
+      </c>
+      <c r="G377" s="1">
+        <v>110.1</v>
+      </c>
+      <c r="H377" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="378" customHeight="1" spans="1:8">
+      <c r="A378" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B378" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C378" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D378" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E378" s="1">
+        <v>122.2</v>
+      </c>
+      <c r="F378" s="1">
+        <v>-16.3</v>
+      </c>
+      <c r="G378" s="1">
+        <v>110.1</v>
+      </c>
+      <c r="H378" s="1">
+        <v>10.9</v>
       </c>
     </row>
   </sheetData>
